--- a/HR_Capstone_Completed_Ishaq Ajayi Ismail.xlsx
+++ b/HR_Capstone_Completed_Ishaq Ajayi Ismail.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sir easynett\Desktop\PROJECTS\Excel-Capstone-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E9EC61-4095-4931-8096-E6DEF6C6922E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2371F28-0BFA-4C45-8760-40FC8C247A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="757" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="757" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Employee_Data" sheetId="1" r:id="rId1"/>
@@ -1123,22 +1123,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf/>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
@@ -1147,6 +1132,9 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1223,13 +1211,22 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Slicer Style 1" pivot="0" table="0" count="1" xr9:uid="{50DB2953-3C0C-499C-B4AD-59CCE3D1450D}">
-      <tableStyleElement type="wholeTable" dxfId="1"/>
-    </tableStyle>
+    <tableStyle name="Slicer Style 1" pivot="0" table="0" count="0" xr9:uid="{50DB2953-3C0C-499C-B4AD-59CCE3D1450D}"/>
     <tableStyle name="Slicer Style 2" pivot="0" table="0" count="1" xr9:uid="{A01612D1-47D9-4ABF-BAE5-952FC6691A2E}">
-      <tableStyleElement type="wholeTable" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="17"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3728,6 +3725,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-1ADF-43FE-97A9-4EEC839AD26D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -3743,6 +3745,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-1ADF-43FE-97A9-4EEC839AD26D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -3758,6 +3765,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-1ADF-43FE-97A9-4EEC839AD26D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -3773,6 +3785,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-1ADF-43FE-97A9-4EEC839AD26D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -3788,6 +3805,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-1ADF-43FE-97A9-4EEC839AD26D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -3803,6 +3825,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-1ADF-43FE-97A9-4EEC839AD26D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -4126,7 +4153,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000036-82CE-478B-876A-44A67BFDE82C}"/>
+              <c16:uniqueId val="{00000024-C3E5-428E-95CA-61B4096760B5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6985,6 +7012,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-2E35-4183-889D-FC09EFEF907E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -7000,6 +7032,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-2E35-4183-889D-FC09EFEF907E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -7015,6 +7052,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-2E35-4183-889D-FC09EFEF907E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -7030,6 +7072,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-2E35-4183-889D-FC09EFEF907E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -7045,6 +7092,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-2E35-4183-889D-FC09EFEF907E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -7060,6 +7112,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-2E35-4183-889D-FC09EFEF907E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -7383,7 +7440,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000032-8A56-471A-8F65-7A3099CA644F}"/>
+              <c16:uniqueId val="{00000025-C596-4C27-A1E4-3384045E4F1E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -16169,8 +16226,8 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="37" name="Department Name 1">
@@ -16193,7 +16250,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -16247,8 +16304,8 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>113393</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="38" name="Years of Service 1">
@@ -16271,7 +16328,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -16325,8 +16382,8 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="39" name="Performance Band 1">
@@ -16349,7 +16406,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -19025,8 +19082,8 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="37" name="Department Name 2">
@@ -19049,7 +19106,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -19103,8 +19160,8 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>113393</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="38" name="Years of Service 2">
@@ -19127,7 +19184,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -19181,8 +19238,8 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="39" name="Performance Band 2">
@@ -19205,7 +19262,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -21681,6 +21738,415 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C0937749-FC8F-46EC-B45B-AB102863D7AB}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A23:B27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Emp ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{72C81AA0-FD8A-4D61-92A2-07E6D0B248DD}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="11">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Emp ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{65BA7A1E-6D3D-443B-946D-DE6A99379C3C}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
+  <location ref="F15:G21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Eligible Bonus Amount" fld="9" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="0">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="10" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{827861A1-C0C4-4642-B039-3D69CEC55446}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19">
+  <location ref="C15:D19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Perf_Score" fld="7" subtotal="average" baseField="10" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="2">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="9" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="18" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{13C2AC3E-FC15-4105-A80D-FB9802B5E81B}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24">
   <location ref="F3:J11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="11">
@@ -22822,7 +23288,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B0409C3-1027-4891-8CAE-E0054DC91A26}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
   <location ref="C3:D10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
@@ -22920,7 +23386,7 @@
     <dataField name="Average of Salary" fld="6" subtotal="average" baseField="3" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="2">
+    <format dxfId="3">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -22953,415 +23419,6 @@
       </pivotArea>
     </chartFormat>
     <chartFormat chart="17" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C0937749-FC8F-46EC-B45B-AB102863D7AB}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A23:B27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Emp ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{72C81AA0-FD8A-4D61-92A2-07E6D0B248DD}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="11">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Emp ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{65BA7A1E-6D3D-443B-946D-DE6A99379C3C}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
-  <location ref="F15:G21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Eligible Bonus Amount" fld="9" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="4">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="10" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{827861A1-C0C4-4642-B039-3D69CEC55446}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19">
-  <location ref="C15:D19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Perf_Score" fld="7" subtotal="average" baseField="10" baseItem="0" numFmtId="2"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="5">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="9" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="18" format="4" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -23463,7 +23520,7 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Department Name 1" xr10:uid="{2CE84CD3-760E-4008-BCD2-40080FB59858}" cache="Slicer_Department_Name" caption="Department Name" rowHeight="241300"/>
+  <slicer name="Department Name 1" xr10:uid="{2CE84CD3-760E-4008-BCD2-40080FB59858}" cache="Slicer_Department_Name" caption="Department Name" startItem="1" rowHeight="241300"/>
   <slicer name="Years of Service 1" xr10:uid="{4E6D8DD2-44D3-4FEF-A050-D7DEFCA64824}" cache="Slicer_Years_of_Service" caption="Years of Service" rowHeight="241300"/>
   <slicer name="Performance Band 1" xr10:uid="{1352F9C4-24D1-4B3F-8D02-74E62F286EFD}" cache="Slicer_Performance_Band" caption="Performance Band" rowHeight="241300"/>
 </slicers>
@@ -23478,28 +23535,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F3703B8F-0939-4E89-BCB3-0D27B443B432}" name="Table1" displayName="Table1" ref="A1:K151" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F3703B8F-0939-4E89-BCB3-0D27B443B432}" name="Table1" displayName="Table1" ref="A1:K151" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="15" tableBorderDxfId="14">
   <autoFilter ref="A1:K151" xr:uid="{F3703B8F-0939-4E89-BCB3-0D27B443B432}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{8FB39840-B6F9-40F4-B174-36648DB9CA7D}" name="Emp ID"/>
-    <tableColumn id="9" xr3:uid="{712CBA6B-7F46-42C0-BC8F-3F3A17B33784}" name="Full Name" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{84433E98-0560-40CE-B7BF-3317B82DB7FC}" name="Dept Code" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{EE55AF4C-9966-4508-B043-DA373B10ABA8}" name="Department Name" dataDxfId="13">
+    <tableColumn id="9" xr3:uid="{712CBA6B-7F46-42C0-BC8F-3F3A17B33784}" name="Full Name" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{84433E98-0560-40CE-B7BF-3317B82DB7FC}" name="Dept Code" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{EE55AF4C-9966-4508-B043-DA373B10ABA8}" name="Department Name" dataDxfId="11">
       <calculatedColumnFormula>VLOOKUP(Table1[[#This Row],[Dept Code]],Lookup_Departments!$A$1:$B$7,2,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{29E8701D-83DA-45C7-AA5E-4DC22823E306}" name="Hire Date" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{7B6A7DE7-5963-4EA1-974F-ED99DC2A2299}" name="Years of Service" dataDxfId="11">
+    <tableColumn id="5" xr3:uid="{29E8701D-83DA-45C7-AA5E-4DC22823E306}" name="Hire Date" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{7B6A7DE7-5963-4EA1-974F-ED99DC2A2299}" name="Years of Service" dataDxfId="9">
       <calculatedColumnFormula>DATEDIF(E2,TODAY(),"Y")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{E1C6B182-21F8-4C94-B35F-6E1D39A5B8D5}" name="Salary" dataDxfId="10" dataCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{2D7B1CBF-BB81-46DF-99B3-EA51BE4AC611}" name="Perf_Score" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{B612875A-C494-4FE4-966B-7FD241BB0798}" name="Performance Band" dataDxfId="8">
+    <tableColumn id="12" xr3:uid="{E1C6B182-21F8-4C94-B35F-6E1D39A5B8D5}" name="Salary" dataDxfId="8" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{2D7B1CBF-BB81-46DF-99B3-EA51BE4AC611}" name="Perf_Score" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{B612875A-C494-4FE4-966B-7FD241BB0798}" name="Performance Band" dataDxfId="6">
       <calculatedColumnFormula>VLOOKUP(H2,Lookup_Performance!$A$2:$D$6,3,TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B14134F1-9ACB-456E-B60F-55BC5BE423F8}" name="Eligible Bonus Amount" dataDxfId="7">
+    <tableColumn id="8" xr3:uid="{B14134F1-9ACB-456E-B60F-55BC5BE423F8}" name="Eligible Bonus Amount" dataDxfId="5">
       <calculatedColumnFormula>IFERROR(G2*VLOOKUP(H2,Lookup_Performance!$A$2:$D$6,4,TRUE),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7D231F97-FD0C-4D56-965B-F4D7E48C56F6}" name="Employment Status" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{7D231F97-FD0C-4D56-965B-F4D7E48C56F6}" name="Employment Status" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -29874,7 +29931,7 @@
   <dimension ref="A2:K27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
